--- a/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_4.xlsx
@@ -7772,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
